--- a/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP_PYRAD/results.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.69 ± 0.11</t>
+          <t>0.70 ± 0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77 ± 0.16</t>
+          <t>0.78 ± 0.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.61 ± 0.13</t>
+          <t>0.63 ± 0.14</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.37 ± 0.23</t>
+          <t>0.36 ± 0.22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.77 ± 0.17</t>
+          <t>0.76 ± 0.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="F4" t="n">
